--- a/output/Data and Chart Outputs/giignl_contracted_vs_spot_annual.xlsx
+++ b/output/Data and Chart Outputs/giignl_contracted_vs_spot_annual.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Units" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,13 +141,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -157,6 +157,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -171,10 +172,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A78D6"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -199,10 +200,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EB6834"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -227,10 +228,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1BAF7A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -255,10 +256,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="EDA100"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -283,10 +284,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="E87BA4"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -311,10 +312,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="008300"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -339,10 +340,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="4A3AA7"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -369,11 +370,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="yyyy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="1"/>
@@ -390,8 +403,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -401,13 +414,14 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
       <spPr>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -415,12 +429,13 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:ln>
       <a:noFill/>
       <a:prstDash val="solid"/>
     </a:ln>
@@ -429,7 +444,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -444,9 +459,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -771,6 +786,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -785,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -799,6 +816,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -813,6 +831,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/giignl_contracted_vs_spot_annual.xlsx
+++ b/output/Data and Chart Outputs/giignl_contracted_vs_spot_annual.xlsx
@@ -152,6 +152,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>LNG exports by country (GIIGNL) (to 2026)</a:t>
             </a:r>
           </a:p>
